--- a/3. NCU Complete -Men's- Starring List from 1st June.xlsx
+++ b/3. NCU Complete -Men's- Starring List from 1st June.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Downloads\Python Environment\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17730" windowHeight="14955" tabRatio="841" firstSheet="25" activeTab="30"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17730" windowHeight="14955" tabRatio="841" firstSheet="23" activeTab="30"/>
   </bookViews>
   <sheets>
     <sheet name="Amigos Belfast" sheetId="6" r:id="rId1"/>
@@ -2903,12 +2903,6 @@
     <t>Thakur</t>
   </si>
   <si>
-    <t xml:space="preserve">Jifin </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Byshal </t>
-  </si>
-  <si>
     <t>Varughese</t>
   </si>
   <si>
@@ -3056,12 +3050,6 @@
     <t>Don</t>
   </si>
   <si>
-    <t xml:space="preserve">Scaria </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ajith </t>
-  </si>
-  <si>
     <t>BATES</t>
   </si>
   <si>
@@ -3290,12 +3278,6 @@
     <t>Cousins</t>
   </si>
   <si>
-    <t>Nagari</t>
-  </si>
-  <si>
-    <t>Veerendra babu</t>
-  </si>
-  <si>
     <t>Venkateswararao</t>
   </si>
   <si>
@@ -3548,17 +3530,35 @@
     <t>Dev</t>
   </si>
   <si>
-    <t>Siyad Muhammad</t>
-  </si>
-  <si>
-    <t>Hafiz</t>
+    <t>Srinuvasarao</t>
+  </si>
+  <si>
+    <t>Nadakuditi</t>
+  </si>
+  <si>
+    <t>Muhammed</t>
+  </si>
+  <si>
+    <t>Jifin</t>
+  </si>
+  <si>
+    <t>Byshal</t>
+  </si>
+  <si>
+    <t>Ajith</t>
+  </si>
+  <si>
+    <t>Scaria</t>
+  </si>
+  <si>
+    <t>Hafis Siyad</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3678,12 +3678,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4462,11 +4456,11 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -4481,7 +4475,7 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
@@ -4490,7 +4484,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -4531,9 +4525,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -4704,7 +4698,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4828,10 +4822,22 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -4851,18 +4857,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5436,7 +5430,7 @@
       <c r="C4" s="210"/>
       <c r="D4" s="210"/>
       <c r="E4" s="210" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="F4" s="210"/>
       <c r="G4" s="210"/>
@@ -5499,7 +5493,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="219" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="C8" s="219"/>
       <c r="D8" s="219"/>
@@ -5589,7 +5583,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="216" t="s">
-        <v>1088</v>
+        <v>1082</v>
       </c>
       <c r="C14" s="216"/>
       <c r="D14" s="216"/>
@@ -5606,12 +5600,12 @@
         <v>2</v>
       </c>
       <c r="B15" s="210" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="C15" s="210"/>
       <c r="D15" s="210"/>
       <c r="E15" s="210" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="F15" s="210"/>
       <c r="G15" s="210"/>
@@ -5640,12 +5634,12 @@
         <v>4</v>
       </c>
       <c r="B17" s="210" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C17" s="210"/>
       <c r="D17" s="210"/>
       <c r="E17" s="210" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="F17" s="210"/>
       <c r="G17" s="210"/>
@@ -5657,7 +5651,7 @@
         <v>5</v>
       </c>
       <c r="B18" s="228" t="s">
-        <v>1159</v>
+        <v>1153</v>
       </c>
       <c r="C18" s="228"/>
       <c r="D18" s="228"/>
@@ -5674,12 +5668,12 @@
         <v>6</v>
       </c>
       <c r="B19" s="228" t="s">
-        <v>1160</v>
+        <v>1154</v>
       </c>
       <c r="C19" s="228"/>
       <c r="D19" s="228"/>
       <c r="E19" s="228" t="s">
-        <v>1161</v>
+        <v>1155</v>
       </c>
       <c r="F19" s="228"/>
       <c r="G19" s="228"/>
@@ -5691,7 +5685,7 @@
         <v>7</v>
       </c>
       <c r="B20" s="210" t="s">
-        <v>1091</v>
+        <v>1085</v>
       </c>
       <c r="C20" s="210"/>
       <c r="D20" s="210"/>
@@ -5725,12 +5719,12 @@
         <v>9</v>
       </c>
       <c r="B22" s="210" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="C22" s="210"/>
       <c r="D22" s="210"/>
       <c r="E22" s="210" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="F22" s="210"/>
       <c r="G22" s="210"/>
@@ -5747,7 +5741,7 @@
       <c r="C23" s="230"/>
       <c r="D23" s="230"/>
       <c r="E23" s="230" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="F23" s="230"/>
       <c r="G23" s="230"/>
@@ -6282,12 +6276,12 @@
         <v>4</v>
       </c>
       <c r="B30" s="345" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="C30" s="345"/>
       <c r="D30" s="345"/>
       <c r="E30" s="345" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="F30" s="345"/>
       <c r="G30" s="345"/>
@@ -6440,12 +6434,12 @@
         <v>3</v>
       </c>
       <c r="B40" s="349" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C40" s="349"/>
       <c r="D40" s="349"/>
       <c r="E40" s="349" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="F40" s="349"/>
       <c r="G40" s="349"/>
@@ -6495,12 +6489,12 @@
         <v>6</v>
       </c>
       <c r="B43" s="349" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C43" s="349"/>
       <c r="D43" s="349"/>
       <c r="E43" s="349" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="F43" s="349"/>
       <c r="G43" s="349"/>
@@ -6666,7 +6660,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="216" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="C3" s="216"/>
       <c r="D3" s="216"/>
@@ -6892,12 +6886,12 @@
         <v>4</v>
       </c>
       <c r="B17" s="349" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="C17" s="349"/>
       <c r="D17" s="349"/>
       <c r="E17" s="349" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="F17" s="349"/>
       <c r="G17" s="349"/>
@@ -7529,7 +7523,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="345" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="C30" s="345"/>
       <c r="D30" s="345"/>
@@ -7565,7 +7559,7 @@
         <v>6</v>
       </c>
       <c r="B32" s="345" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="C32" s="345"/>
       <c r="D32" s="345"/>
@@ -7689,12 +7683,12 @@
         <v>3</v>
       </c>
       <c r="B40" s="348" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
       <c r="C40" s="348"/>
       <c r="D40" s="348"/>
       <c r="E40" s="348" t="s">
-        <v>1111</v>
+        <v>1105</v>
       </c>
       <c r="F40" s="348"/>
       <c r="G40" s="348"/>
@@ -7740,7 +7734,7 @@
         <v>6</v>
       </c>
       <c r="B43" s="348" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="C43" s="348"/>
       <c r="D43" s="348"/>
@@ -8072,7 +8066,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="216" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="C14" s="216"/>
       <c r="D14" s="216"/>
@@ -8106,7 +8100,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="228" t="s">
-        <v>1114</v>
+        <v>1108</v>
       </c>
       <c r="C16" s="228"/>
       <c r="D16" s="228"/>
@@ -8128,7 +8122,7 @@
       <c r="C17" s="219"/>
       <c r="D17" s="219"/>
       <c r="E17" s="219" t="s">
-        <v>1115</v>
+        <v>1109</v>
       </c>
       <c r="F17" s="219"/>
       <c r="G17" s="219"/>
@@ -8196,7 +8190,7 @@
       <c r="C21" s="219"/>
       <c r="D21" s="219"/>
       <c r="E21" s="219" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="F21" s="219"/>
       <c r="G21" s="219"/>
@@ -8315,7 +8309,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="219" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="C29" s="219"/>
       <c r="D29" s="219"/>
@@ -8400,12 +8394,12 @@
         <v>8</v>
       </c>
       <c r="B34" s="219" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="C34" s="219"/>
       <c r="D34" s="219"/>
       <c r="E34" s="219" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="F34" s="219"/>
       <c r="G34" s="219"/>
@@ -8473,12 +8467,12 @@
         <v>2</v>
       </c>
       <c r="B39" s="228" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
       <c r="C39" s="228"/>
       <c r="D39" s="228"/>
       <c r="E39" s="228" t="s">
-        <v>1117</v>
+        <v>1111</v>
       </c>
       <c r="F39" s="228"/>
       <c r="G39" s="228"/>
@@ -8529,7 +8523,7 @@
       <c r="C42" s="228"/>
       <c r="D42" s="228"/>
       <c r="E42" s="228" t="s">
-        <v>1118</v>
+        <v>1112</v>
       </c>
       <c r="F42" s="228"/>
       <c r="G42" s="228"/>
@@ -9115,12 +9109,12 @@
         <v>3</v>
       </c>
       <c r="B29" s="348" t="s">
-        <v>1119</v>
+        <v>1113</v>
       </c>
       <c r="C29" s="348"/>
       <c r="D29" s="348"/>
       <c r="E29" s="348" t="s">
-        <v>1120</v>
+        <v>1114</v>
       </c>
       <c r="F29" s="348"/>
       <c r="G29" s="348"/>
@@ -9325,7 +9319,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="355" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="C3" s="355"/>
       <c r="D3" s="355"/>
@@ -9342,7 +9336,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="353" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="C4" s="353"/>
       <c r="D4" s="353"/>
@@ -9376,7 +9370,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="353" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="C6" s="353"/>
       <c r="D6" s="353"/>
@@ -9393,7 +9387,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="353" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="C7" s="353"/>
       <c r="D7" s="353"/>
@@ -9410,7 +9404,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="353" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="C8" s="353"/>
       <c r="D8" s="353"/>
@@ -9427,7 +9421,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="353" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="C9" s="353"/>
       <c r="D9" s="353"/>
@@ -9444,7 +9438,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="228" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="C10" s="228"/>
       <c r="D10" s="228"/>
@@ -9500,7 +9494,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="355" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="C14" s="355"/>
       <c r="D14" s="355"/>
@@ -9517,7 +9511,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="353" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="C15" s="353"/>
       <c r="D15" s="353"/>
@@ -9534,7 +9528,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="353" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="C16" s="353"/>
       <c r="D16" s="353"/>
@@ -9551,7 +9545,7 @@
         <v>4</v>
       </c>
       <c r="B17" s="353" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="C17" s="353"/>
       <c r="D17" s="353"/>
@@ -9568,7 +9562,7 @@
         <v>5</v>
       </c>
       <c r="B18" s="353" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C18" s="353"/>
       <c r="D18" s="353"/>
@@ -9585,7 +9579,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="353" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="C19" s="353"/>
       <c r="D19" s="353"/>
@@ -9602,12 +9596,12 @@
         <v>7</v>
       </c>
       <c r="B20" s="219" t="s">
-        <v>1100</v>
+        <v>1094</v>
       </c>
       <c r="C20" s="219"/>
       <c r="D20" s="219"/>
       <c r="E20" s="219" t="s">
-        <v>1101</v>
+        <v>1095</v>
       </c>
       <c r="F20" s="219"/>
       <c r="G20" s="219"/>
@@ -9619,7 +9613,7 @@
         <v>8</v>
       </c>
       <c r="B21" s="353" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C21" s="353"/>
       <c r="D21" s="353"/>
@@ -9653,7 +9647,7 @@
         <v>10</v>
       </c>
       <c r="B23" s="228" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C23" s="228"/>
       <c r="D23" s="228"/>
@@ -9709,7 +9703,7 @@
         <v>1</v>
       </c>
       <c r="B27" s="216" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="C27" s="216"/>
       <c r="D27" s="216"/>
@@ -9726,7 +9720,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="219" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="C28" s="219"/>
       <c r="D28" s="219"/>
@@ -9743,7 +9737,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="353" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C29" s="353"/>
       <c r="D29" s="353"/>
@@ -9760,12 +9754,12 @@
         <v>4</v>
       </c>
       <c r="B30" s="348" t="s">
-        <v>1147</v>
+        <v>1141</v>
       </c>
       <c r="C30" s="348"/>
       <c r="D30" s="348"/>
       <c r="E30" s="348" t="s">
-        <v>1102</v>
+        <v>1096</v>
       </c>
       <c r="F30" s="348"/>
       <c r="G30" s="348"/>
@@ -9777,12 +9771,12 @@
         <v>5</v>
       </c>
       <c r="B31" s="219" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="C31" s="219"/>
       <c r="D31" s="219"/>
       <c r="E31" s="219" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="F31" s="219"/>
       <c r="G31" s="219"/>
@@ -9794,7 +9788,7 @@
         <v>6</v>
       </c>
       <c r="B32" s="219" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="C32" s="219"/>
       <c r="D32" s="219"/>
@@ -9811,12 +9805,12 @@
         <v>7</v>
       </c>
       <c r="B33" s="219" t="s">
-        <v>1102</v>
+        <v>1096</v>
       </c>
       <c r="C33" s="219"/>
       <c r="D33" s="219"/>
       <c r="E33" s="219" t="s">
-        <v>1103</v>
+        <v>1097</v>
       </c>
       <c r="F33" s="219"/>
       <c r="G33" s="219"/>
@@ -10051,12 +10045,12 @@
         <v>7</v>
       </c>
       <c r="B9" s="360" t="s">
-        <v>1148</v>
+        <v>1142</v>
       </c>
       <c r="C9" s="360"/>
       <c r="D9" s="360"/>
       <c r="E9" s="360" t="s">
-        <v>1149</v>
+        <v>1143</v>
       </c>
       <c r="F9" s="360"/>
       <c r="G9" s="360"/>
@@ -10458,12 +10452,12 @@
         <v>8</v>
       </c>
       <c r="B34" s="240" t="s">
-        <v>1150</v>
+        <v>1144</v>
       </c>
       <c r="C34" s="240"/>
       <c r="D34" s="240"/>
       <c r="E34" s="240" t="s">
-        <v>1151</v>
+        <v>1145</v>
       </c>
       <c r="F34" s="240"/>
       <c r="G34" s="240"/>
@@ -10790,7 +10784,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="347" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="C5" s="347"/>
       <c r="D5" s="347"/>
@@ -10948,7 +10942,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="348" t="s">
-        <v>1084</v>
+        <v>1078</v>
       </c>
       <c r="C15" s="348"/>
       <c r="D15" s="348"/>
@@ -11016,7 +11010,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="348" t="s">
-        <v>1085</v>
+        <v>1079</v>
       </c>
       <c r="C19" s="348"/>
       <c r="D19" s="348"/>
@@ -11376,7 +11370,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="228" t="s">
-        <v>1138</v>
+        <v>1132</v>
       </c>
       <c r="C15" s="228"/>
       <c r="D15" s="228"/>
@@ -11427,12 +11421,12 @@
         <v>5</v>
       </c>
       <c r="B18" s="210" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="C18" s="210"/>
       <c r="D18" s="210"/>
       <c r="E18" s="210" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="F18" s="210"/>
       <c r="G18" s="210"/>
@@ -11663,12 +11657,12 @@
         <v>4</v>
       </c>
       <c r="B6" s="384" t="s">
-        <v>1126</v>
+        <v>1120</v>
       </c>
       <c r="C6" s="384"/>
       <c r="D6" s="137"/>
       <c r="E6" s="384" t="s">
-        <v>1127</v>
+        <v>1121</v>
       </c>
       <c r="F6" s="384"/>
       <c r="G6" s="384"/>
@@ -11872,12 +11866,12 @@
         <v>6</v>
       </c>
       <c r="B19" s="391" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="C19" s="391"/>
       <c r="D19" s="391"/>
       <c r="E19" s="391" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="F19" s="391"/>
       <c r="G19" s="391"/>
@@ -11928,7 +11922,7 @@
       <c r="C22" s="384"/>
       <c r="D22" s="137"/>
       <c r="E22" s="384" t="s">
-        <v>1128</v>
+        <v>1122</v>
       </c>
       <c r="F22" s="384"/>
       <c r="G22" s="384"/>
@@ -12072,12 +12066,12 @@
         <v>5</v>
       </c>
       <c r="B31" s="380" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="C31" s="399"/>
       <c r="D31" s="399"/>
       <c r="E31" s="380" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="F31" s="399"/>
       <c r="G31" s="399"/>
@@ -12108,12 +12102,12 @@
         <v>7</v>
       </c>
       <c r="B33" s="210" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="C33" s="210"/>
       <c r="D33" s="210"/>
       <c r="E33" s="210" t="s">
-        <v>1109</v>
+        <v>1103</v>
       </c>
       <c r="F33" s="210"/>
       <c r="G33" s="210"/>
@@ -12270,7 +12264,7 @@
       <c r="C4" s="232"/>
       <c r="D4" s="232"/>
       <c r="E4" s="210" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="F4" s="232"/>
       <c r="G4" s="232"/>
@@ -12299,12 +12293,12 @@
         <v>4</v>
       </c>
       <c r="B6" s="240" t="s">
-        <v>1076</v>
+        <v>1157</v>
       </c>
       <c r="C6" s="241"/>
       <c r="D6" s="241"/>
       <c r="E6" s="242" t="s">
-        <v>1077</v>
+        <v>1156</v>
       </c>
       <c r="F6" s="243"/>
       <c r="G6" s="243"/>
@@ -12321,7 +12315,7 @@
       <c r="C7" s="232"/>
       <c r="D7" s="232"/>
       <c r="E7" s="210" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="F7" s="232"/>
       <c r="G7" s="232"/>
@@ -12333,12 +12327,12 @@
         <v>6</v>
       </c>
       <c r="B8" s="210" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="C8" s="232"/>
       <c r="D8" s="232"/>
       <c r="E8" s="210" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="F8" s="232"/>
       <c r="G8" s="232"/>
@@ -12350,12 +12344,12 @@
         <v>7</v>
       </c>
       <c r="B9" s="210" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="C9" s="232"/>
       <c r="D9" s="232"/>
       <c r="E9" s="210" t="s">
-        <v>1079</v>
+        <v>1073</v>
       </c>
       <c r="F9" s="232"/>
       <c r="G9" s="232"/>
@@ -12372,7 +12366,7 @@
       <c r="C10" s="246"/>
       <c r="D10" s="246"/>
       <c r="E10" s="245" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="F10" s="246"/>
       <c r="G10" s="246"/>
@@ -12482,7 +12476,7 @@
       <c r="C5" s="409"/>
       <c r="D5" s="409"/>
       <c r="E5" s="410" t="s">
-        <v>1144</v>
+        <v>1138</v>
       </c>
       <c r="F5" s="410"/>
       <c r="G5" s="410"/>
@@ -12562,12 +12556,12 @@
         <v>8</v>
       </c>
       <c r="B10" s="412" t="s">
-        <v>1145</v>
+        <v>1139</v>
       </c>
       <c r="C10" s="412"/>
       <c r="D10" s="412"/>
       <c r="E10" s="412" t="s">
-        <v>1146</v>
+        <v>1140</v>
       </c>
       <c r="F10" s="412"/>
       <c r="G10" s="412"/>
@@ -12727,12 +12721,12 @@
         <v>6</v>
       </c>
       <c r="B8" s="262" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="C8" s="262"/>
       <c r="D8" s="262"/>
       <c r="E8" s="219" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="F8" s="219"/>
       <c r="G8" s="219"/>
@@ -12744,7 +12738,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="240" t="s">
-        <v>1085</v>
+        <v>1079</v>
       </c>
       <c r="C9" s="240"/>
       <c r="D9" s="240"/>
@@ -12761,7 +12755,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="245" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="C10" s="245"/>
       <c r="D10" s="245"/>
@@ -12905,12 +12899,12 @@
         <v>5</v>
       </c>
       <c r="B7" s="228" t="s">
-        <v>1153</v>
+        <v>1147</v>
       </c>
       <c r="C7" s="228"/>
       <c r="D7" s="228"/>
       <c r="E7" s="228" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="F7" s="228"/>
       <c r="G7" s="228"/>
@@ -12963,7 +12957,7 @@
       <c r="C10" s="257"/>
       <c r="D10" s="257"/>
       <c r="E10" s="257" t="s">
-        <v>1155</v>
+        <v>1149</v>
       </c>
       <c r="F10" s="257"/>
       <c r="G10" s="257"/>
@@ -13070,7 +13064,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="262" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="C5" s="262"/>
       <c r="D5" s="262"/>
@@ -13104,12 +13098,12 @@
         <v>5</v>
       </c>
       <c r="B7" s="210" t="s">
-        <v>1104</v>
+        <v>1098</v>
       </c>
       <c r="C7" s="210"/>
       <c r="D7" s="210"/>
       <c r="E7" s="210" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="F7" s="210"/>
       <c r="G7" s="210"/>
@@ -13155,12 +13149,12 @@
         <v>8</v>
       </c>
       <c r="B10" s="210" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="C10" s="210"/>
       <c r="D10" s="210"/>
       <c r="E10" s="210" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="F10" s="210"/>
       <c r="G10" s="210"/>
@@ -13296,12 +13290,12 @@
         <v>6</v>
       </c>
       <c r="B19" s="228" t="s">
-        <v>1131</v>
+        <v>1125</v>
       </c>
       <c r="C19" s="228"/>
       <c r="D19" s="228"/>
       <c r="E19" s="228" t="s">
-        <v>1132</v>
+        <v>1126</v>
       </c>
       <c r="F19" s="228"/>
       <c r="G19" s="228"/>
@@ -13493,7 +13487,7 @@
       <c r="C31" s="228"/>
       <c r="D31" s="228"/>
       <c r="E31" s="228" t="s">
-        <v>1133</v>
+        <v>1127</v>
       </c>
       <c r="F31" s="228"/>
       <c r="G31" s="228"/>
@@ -13527,7 +13521,7 @@
       <c r="C33" s="210"/>
       <c r="D33" s="210"/>
       <c r="E33" s="210" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="F33" s="210"/>
       <c r="G33" s="210"/>
@@ -13840,12 +13834,12 @@
         <v>1</v>
       </c>
       <c r="B15" s="248" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="C15" s="248"/>
       <c r="D15" s="248"/>
       <c r="E15" s="248" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="F15" s="248"/>
       <c r="G15" s="248"/>
@@ -13879,7 +13873,7 @@
       <c r="C17" s="210"/>
       <c r="D17" s="210"/>
       <c r="E17" s="210" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="F17" s="210"/>
       <c r="G17" s="210"/>
@@ -13891,7 +13885,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="210" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="C18" s="210"/>
       <c r="D18" s="210"/>
@@ -13942,12 +13936,12 @@
         <v>7</v>
       </c>
       <c r="B21" s="423" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
       <c r="C21" s="423"/>
       <c r="D21" s="423"/>
       <c r="E21" s="423" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="F21" s="423"/>
       <c r="G21" s="423"/>
@@ -14337,12 +14331,12 @@
         <v>5</v>
       </c>
       <c r="B18" s="210" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="C18" s="210"/>
       <c r="D18" s="210"/>
       <c r="E18" s="210" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="F18" s="210"/>
       <c r="G18" s="210"/>
@@ -14517,7 +14511,7 @@
       <c r="C29" s="210"/>
       <c r="D29" s="210"/>
       <c r="E29" s="210" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="F29" s="210"/>
       <c r="G29" s="210"/>
@@ -14580,7 +14574,7 @@
         <v>7</v>
       </c>
       <c r="B33" s="228" t="s">
-        <v>1152</v>
+        <v>1146</v>
       </c>
       <c r="C33" s="228"/>
       <c r="D33" s="228"/>
@@ -14984,7 +14978,7 @@
       <c r="C8" s="345"/>
       <c r="D8" s="345"/>
       <c r="E8" s="345" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="F8" s="345"/>
       <c r="G8" s="345"/>
@@ -14996,12 +14990,12 @@
         <v>7</v>
       </c>
       <c r="B9" s="348" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="C9" s="348"/>
       <c r="D9" s="348"/>
       <c r="E9" s="348" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="F9" s="348"/>
       <c r="G9" s="348"/>
@@ -15384,7 +15378,7 @@
         <v>8</v>
       </c>
       <c r="B21" s="425" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="C21" s="425"/>
       <c r="D21" s="425"/>
@@ -15401,7 +15395,7 @@
         <v>9</v>
       </c>
       <c r="B22" s="425" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="C22" s="425"/>
       <c r="D22" s="425"/>
@@ -15518,12 +15512,12 @@
         <v>1</v>
       </c>
       <c r="B3" s="248" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="C3" s="248"/>
       <c r="D3" s="171"/>
       <c r="E3" s="248" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="F3" s="248"/>
       <c r="G3" s="248"/>
@@ -16111,7 +16105,7 @@
         <v>3</v>
       </c>
       <c r="B40" s="219" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="C40" s="219"/>
       <c r="D40" s="160"/>
@@ -16133,7 +16127,7 @@
       <c r="C41" s="219"/>
       <c r="D41" s="160"/>
       <c r="E41" s="219" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="F41" s="219"/>
       <c r="G41" s="219"/>
@@ -16167,7 +16161,7 @@
       <c r="C43" s="228"/>
       <c r="D43" s="154"/>
       <c r="E43" s="228" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="F43" s="228"/>
       <c r="G43" s="228"/>
@@ -16179,7 +16173,7 @@
         <v>7</v>
       </c>
       <c r="B44" s="245" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="C44" s="245"/>
       <c r="D44" s="166"/>
@@ -16826,12 +16820,12 @@
         <v>8</v>
       </c>
       <c r="B34" s="429" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="C34" s="430"/>
       <c r="D34" s="430"/>
       <c r="E34" s="429" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="F34" s="430"/>
       <c r="G34" s="430"/>
@@ -16950,12 +16944,12 @@
         <v>1</v>
       </c>
       <c r="B3" s="248" t="s">
-        <v>1134</v>
+        <v>1128</v>
       </c>
       <c r="C3" s="248"/>
       <c r="D3" s="248"/>
       <c r="E3" s="248" t="s">
-        <v>1135</v>
+        <v>1129</v>
       </c>
       <c r="F3" s="248"/>
       <c r="G3" s="248"/>
@@ -16972,7 +16966,7 @@
       <c r="C4" s="210"/>
       <c r="D4" s="210"/>
       <c r="E4" s="210" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="F4" s="210"/>
       <c r="G4" s="210"/>
@@ -17040,7 +17034,7 @@
       <c r="C8" s="210"/>
       <c r="D8" s="210"/>
       <c r="E8" s="210" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="F8" s="210"/>
       <c r="G8" s="210"/>
@@ -17052,7 +17046,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="210" t="s">
-        <v>1136</v>
+        <v>1130</v>
       </c>
       <c r="C9" s="210"/>
       <c r="D9" s="210"/>
@@ -17261,7 +17255,7 @@
         <v>9</v>
       </c>
       <c r="B22" s="210" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
       <c r="C22" s="210"/>
       <c r="D22" s="210"/>
@@ -17334,12 +17328,12 @@
         <v>1</v>
       </c>
       <c r="B27" s="254" t="s">
-        <v>1140</v>
+        <v>1134</v>
       </c>
       <c r="C27" s="254"/>
       <c r="D27" s="254"/>
       <c r="E27" s="254" t="s">
-        <v>1096</v>
+        <v>1090</v>
       </c>
       <c r="F27" s="254"/>
       <c r="G27" s="254"/>
@@ -17351,12 +17345,12 @@
         <v>2</v>
       </c>
       <c r="B28" s="219" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="C28" s="219"/>
       <c r="D28" s="219"/>
       <c r="E28" s="219" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="F28" s="219"/>
       <c r="G28" s="219"/>
@@ -17436,7 +17430,7 @@
         <v>7</v>
       </c>
       <c r="B33" s="228" t="s">
-        <v>1143</v>
+        <v>1137</v>
       </c>
       <c r="C33" s="228"/>
       <c r="D33" s="228"/>
@@ -17526,7 +17520,7 @@
         <v>2</v>
       </c>
       <c r="B39" s="219" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="C39" s="219"/>
       <c r="D39" s="219"/>
@@ -17594,12 +17588,12 @@
         <v>6</v>
       </c>
       <c r="B43" s="210" t="s">
-        <v>1097</v>
+        <v>1091</v>
       </c>
       <c r="C43" s="210"/>
       <c r="D43" s="210"/>
       <c r="E43" s="210" t="s">
-        <v>1098</v>
+        <v>1092</v>
       </c>
       <c r="F43" s="210"/>
       <c r="G43" s="210"/>
@@ -17611,12 +17605,12 @@
         <v>7</v>
       </c>
       <c r="B44" s="257" t="s">
-        <v>1141</v>
+        <v>1135</v>
       </c>
       <c r="C44" s="257"/>
       <c r="D44" s="257"/>
       <c r="E44" s="257" t="s">
-        <v>1142</v>
+        <v>1136</v>
       </c>
       <c r="F44" s="257"/>
       <c r="G44" s="257"/>
@@ -18553,12 +18547,12 @@
         <v>6</v>
       </c>
       <c r="B53" s="451" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="C53" s="451"/>
       <c r="D53" s="451"/>
       <c r="E53" s="451" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="F53" s="451"/>
       <c r="G53" s="451"/>
@@ -18726,8 +18720,8 @@
       <c r="A3" s="24">
         <v>1</v>
       </c>
-      <c r="B3" s="479" t="s">
-        <v>949</v>
+      <c r="B3" s="461" t="s">
+        <v>947</v>
       </c>
       <c r="C3" s="216"/>
       <c r="D3" s="216"/>
@@ -18743,13 +18737,13 @@
       <c r="A4" s="25">
         <v>2</v>
       </c>
-      <c r="B4" s="480" t="s">
+      <c r="B4" s="460" t="s">
         <v>152</v>
       </c>
       <c r="C4" s="304"/>
       <c r="D4" s="304"/>
       <c r="E4" s="304" t="s">
-        <v>947</v>
+        <v>1159</v>
       </c>
       <c r="F4" s="304"/>
       <c r="G4" s="304"/>
@@ -18760,13 +18754,13 @@
       <c r="A5" s="64">
         <v>3</v>
       </c>
-      <c r="B5" s="481" t="s">
-        <v>1162</v>
+      <c r="B5" s="462" t="s">
+        <v>1163</v>
       </c>
       <c r="C5" s="372"/>
       <c r="D5" s="372"/>
       <c r="E5" s="372" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="F5" s="372"/>
       <c r="G5" s="372"/>
@@ -18777,13 +18771,13 @@
       <c r="A6" s="25">
         <v>4</v>
       </c>
-      <c r="B6" s="482" t="s">
+      <c r="B6" s="463" t="s">
         <v>131</v>
       </c>
       <c r="C6" s="310"/>
       <c r="D6" s="310"/>
       <c r="E6" s="310" t="s">
-        <v>948</v>
+        <v>1160</v>
       </c>
       <c r="F6" s="310"/>
       <c r="G6" s="310"/>
@@ -18794,7 +18788,7 @@
       <c r="A7" s="78">
         <v>5</v>
       </c>
-      <c r="B7" s="483" t="s">
+      <c r="B7" s="464" t="s">
         <v>152</v>
       </c>
       <c r="C7" s="210"/>
@@ -18811,13 +18805,13 @@
       <c r="A8" s="25">
         <v>6</v>
       </c>
-      <c r="B8" s="483" t="s">
-        <v>1025</v>
+      <c r="B8" s="464" t="s">
+        <v>1021</v>
       </c>
       <c r="C8" s="210"/>
       <c r="D8" s="210"/>
       <c r="E8" s="210" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="F8" s="210"/>
       <c r="G8" s="210"/>
@@ -18828,13 +18822,13 @@
       <c r="A9" s="25">
         <v>7</v>
       </c>
-      <c r="B9" s="482" t="s">
-        <v>998</v>
+      <c r="B9" s="463" t="s">
+        <v>1162</v>
       </c>
       <c r="C9" s="310"/>
       <c r="D9" s="310"/>
       <c r="E9" s="310" t="s">
-        <v>999</v>
+        <v>1161</v>
       </c>
       <c r="F9" s="310"/>
       <c r="G9" s="310"/>
@@ -18845,7 +18839,7 @@
       <c r="A10" s="130">
         <v>8</v>
       </c>
-      <c r="B10" s="484" t="s">
+      <c r="B10" s="465" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="230"/>
@@ -18996,7 +18990,7 @@
       <c r="C7" s="219"/>
       <c r="D7" s="219"/>
       <c r="E7" s="219" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="F7" s="219"/>
       <c r="G7" s="219"/>
@@ -19008,7 +19002,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="210" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="C8" s="210"/>
       <c r="D8" s="210"/>
@@ -19183,7 +19177,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="219" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="C19" s="219"/>
       <c r="D19" s="219"/>
@@ -19324,7 +19318,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="348" t="s">
-        <v>1158</v>
+        <v>1152</v>
       </c>
       <c r="C28" s="348"/>
       <c r="D28" s="348"/>
@@ -19486,12 +19480,12 @@
         <v>1</v>
       </c>
       <c r="B38" s="248" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="C38" s="248"/>
       <c r="D38" s="248"/>
       <c r="E38" s="248" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="F38" s="248"/>
       <c r="G38" s="248"/>
@@ -19504,7 +19498,7 @@
         <v>2</v>
       </c>
       <c r="B39" s="210" t="s">
-        <v>1123</v>
+        <v>1117</v>
       </c>
       <c r="C39" s="210"/>
       <c r="D39" s="210"/>
@@ -19558,12 +19552,12 @@
         <v>5</v>
       </c>
       <c r="B42" s="210" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="C42" s="210"/>
       <c r="D42" s="210"/>
       <c r="E42" s="210" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="F42" s="210"/>
       <c r="G42" s="210"/>
@@ -19581,7 +19575,7 @@
       <c r="C43" s="210"/>
       <c r="D43" s="210"/>
       <c r="E43" s="210" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="F43" s="210"/>
       <c r="G43" s="210"/>
@@ -19593,12 +19587,12 @@
         <v>7</v>
       </c>
       <c r="B44" s="210" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="C44" s="210"/>
       <c r="D44" s="210"/>
       <c r="E44" s="210" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="F44" s="210"/>
       <c r="G44" s="210"/>
@@ -19713,7 +19707,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="462" t="s">
+      <c r="A1" s="468" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="389"/>
@@ -19755,129 +19749,129 @@
       <c r="F3" s="389"/>
       <c r="G3" s="389"/>
       <c r="H3" s="389"/>
-      <c r="I3" s="466"/>
+      <c r="I3" s="472"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="10">
         <v>2</v>
       </c>
-      <c r="B4" s="464" t="s">
+      <c r="B4" s="470" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="465"/>
-      <c r="D4" s="465"/>
-      <c r="E4" s="464" t="s">
+      <c r="C4" s="471"/>
+      <c r="D4" s="471"/>
+      <c r="E4" s="470" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="465"/>
-      <c r="G4" s="465"/>
-      <c r="H4" s="465"/>
-      <c r="I4" s="467"/>
+      <c r="F4" s="471"/>
+      <c r="G4" s="471"/>
+      <c r="H4" s="471"/>
+      <c r="I4" s="473"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <v>3</v>
       </c>
-      <c r="B5" s="468" t="s">
+      <c r="B5" s="474" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="465"/>
-      <c r="D5" s="465"/>
-      <c r="E5" s="468" t="s">
+      <c r="C5" s="471"/>
+      <c r="D5" s="471"/>
+      <c r="E5" s="474" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="465"/>
-      <c r="G5" s="465"/>
-      <c r="H5" s="465"/>
-      <c r="I5" s="467"/>
+      <c r="F5" s="471"/>
+      <c r="G5" s="471"/>
+      <c r="H5" s="471"/>
+      <c r="I5" s="473"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <v>4</v>
       </c>
-      <c r="B6" s="464" t="s">
+      <c r="B6" s="470" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="465"/>
-      <c r="D6" s="465"/>
-      <c r="E6" s="464" t="s">
+      <c r="C6" s="471"/>
+      <c r="D6" s="471"/>
+      <c r="E6" s="470" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="465"/>
-      <c r="G6" s="465"/>
-      <c r="H6" s="465"/>
-      <c r="I6" s="467"/>
+      <c r="F6" s="471"/>
+      <c r="G6" s="471"/>
+      <c r="H6" s="471"/>
+      <c r="I6" s="473"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
         <v>5</v>
       </c>
-      <c r="B7" s="464" t="s">
+      <c r="B7" s="470" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="465"/>
-      <c r="D7" s="465"/>
-      <c r="E7" s="464" t="s">
+      <c r="C7" s="471"/>
+      <c r="D7" s="471"/>
+      <c r="E7" s="470" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="465"/>
-      <c r="G7" s="465"/>
-      <c r="H7" s="465"/>
-      <c r="I7" s="467"/>
+      <c r="F7" s="471"/>
+      <c r="G7" s="471"/>
+      <c r="H7" s="471"/>
+      <c r="I7" s="473"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>6</v>
       </c>
-      <c r="B8" s="470" t="s">
-        <v>955</v>
-      </c>
-      <c r="C8" s="470"/>
-      <c r="D8" s="470"/>
-      <c r="E8" s="469" t="s">
-        <v>956</v>
-      </c>
-      <c r="F8" s="469"/>
-      <c r="G8" s="469"/>
-      <c r="H8" s="469"/>
-      <c r="I8" s="469"/>
+      <c r="B8" s="476" t="s">
+        <v>953</v>
+      </c>
+      <c r="C8" s="476"/>
+      <c r="D8" s="476"/>
+      <c r="E8" s="475" t="s">
+        <v>954</v>
+      </c>
+      <c r="F8" s="475"/>
+      <c r="G8" s="475"/>
+      <c r="H8" s="475"/>
+      <c r="I8" s="475"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>7</v>
       </c>
-      <c r="B9" s="464" t="s">
+      <c r="B9" s="470" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="465"/>
-      <c r="D9" s="465"/>
-      <c r="E9" s="464" t="s">
+      <c r="C9" s="471"/>
+      <c r="D9" s="471"/>
+      <c r="E9" s="470" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="465"/>
-      <c r="G9" s="465"/>
-      <c r="H9" s="465"/>
-      <c r="I9" s="467"/>
+      <c r="F9" s="471"/>
+      <c r="G9" s="471"/>
+      <c r="H9" s="471"/>
+      <c r="I9" s="473"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>8</v>
       </c>
-      <c r="B10" s="464" t="s">
+      <c r="B10" s="470" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="465"/>
-      <c r="D10" s="465"/>
-      <c r="E10" s="464" t="s">
+      <c r="C10" s="471"/>
+      <c r="D10" s="471"/>
+      <c r="E10" s="470" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="465"/>
-      <c r="G10" s="465"/>
-      <c r="H10" s="465"/>
-      <c r="I10" s="467"/>
+      <c r="F10" s="471"/>
+      <c r="G10" s="471"/>
+      <c r="H10" s="471"/>
+      <c r="I10" s="473"/>
     </row>
     <row r="11" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="460"/>
+      <c r="A11" s="466"/>
       <c r="B11" s="387"/>
       <c r="C11" s="387"/>
       <c r="D11" s="387"/>
@@ -19885,10 +19879,10 @@
       <c r="F11" s="387"/>
       <c r="G11" s="387"/>
       <c r="H11" s="387"/>
-      <c r="I11" s="461"/>
+      <c r="I11" s="467"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="462" t="s">
+      <c r="A12" s="468" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="389"/>
@@ -19987,18 +19981,18 @@
       <c r="A18" s="207">
         <v>5</v>
       </c>
-      <c r="B18" s="463" t="s">
+      <c r="B18" s="469" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="463"/>
-      <c r="D18" s="463"/>
-      <c r="E18" s="463" t="s">
+      <c r="C18" s="469"/>
+      <c r="D18" s="469"/>
+      <c r="E18" s="469" t="s">
         <v>325</v>
       </c>
-      <c r="F18" s="463"/>
-      <c r="G18" s="463"/>
-      <c r="H18" s="463"/>
-      <c r="I18" s="463"/>
+      <c r="F18" s="469"/>
+      <c r="G18" s="469"/>
+      <c r="H18" s="469"/>
+      <c r="I18" s="469"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="69">
@@ -20010,7 +20004,7 @@
       <c r="C19" s="399"/>
       <c r="D19" s="399"/>
       <c r="E19" s="380" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="F19" s="399"/>
       <c r="G19" s="399"/>
@@ -20022,12 +20016,12 @@
         <v>7</v>
       </c>
       <c r="B20" s="380" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="C20" s="399"/>
       <c r="D20" s="399"/>
       <c r="E20" s="380" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="F20" s="399"/>
       <c r="G20" s="399"/>
@@ -20177,12 +20171,12 @@
         <v>1</v>
       </c>
       <c r="B3" s="248" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="C3" s="248"/>
       <c r="D3" s="248"/>
       <c r="E3" s="248" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="F3" s="248"/>
       <c r="G3" s="248"/>
@@ -20249,7 +20243,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="219" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="C7" s="219"/>
       <c r="D7" s="219"/>
@@ -20677,7 +20671,7 @@
         <v>6</v>
       </c>
       <c r="B32" s="219" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="C32" s="219"/>
       <c r="D32" s="219"/>
@@ -21114,12 +21108,12 @@
         <v>7</v>
       </c>
       <c r="B20" s="228" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="C20" s="228"/>
       <c r="D20" s="228"/>
       <c r="E20" s="228" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="F20" s="228"/>
       <c r="G20" s="228"/>
@@ -21130,11 +21124,11 @@
       <c r="A21" s="25">
         <v>8</v>
       </c>
-      <c r="B21" s="471" t="s">
+      <c r="B21" s="477" t="s">
         <v>875</v>
       </c>
-      <c r="C21" s="471"/>
-      <c r="D21" s="471"/>
+      <c r="C21" s="477"/>
+      <c r="D21" s="477"/>
       <c r="E21" s="219" t="s">
         <v>503</v>
       </c>
@@ -21148,7 +21142,7 @@
         <v>9</v>
       </c>
       <c r="B22" s="210" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="C22" s="210"/>
       <c r="D22" s="210"/>
@@ -21339,18 +21333,18 @@
       <c r="A34" s="97">
         <v>8</v>
       </c>
-      <c r="B34" s="472" t="s">
-        <v>1121</v>
-      </c>
-      <c r="C34" s="472"/>
-      <c r="D34" s="472"/>
-      <c r="E34" s="472" t="s">
-        <v>1122</v>
-      </c>
-      <c r="F34" s="472"/>
-      <c r="G34" s="472"/>
-      <c r="H34" s="472"/>
-      <c r="I34" s="473"/>
+      <c r="B34" s="478" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C34" s="478"/>
+      <c r="D34" s="478"/>
+      <c r="E34" s="478" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F34" s="478"/>
+      <c r="G34" s="478"/>
+      <c r="H34" s="478"/>
+      <c r="I34" s="479"/>
     </row>
   </sheetData>
   <mergeCells count="64">
@@ -21460,18 +21454,18 @@
       <c r="A3" s="107">
         <v>1</v>
       </c>
-      <c r="B3" s="474" t="s">
+      <c r="B3" s="480" t="s">
         <v>894</v>
       </c>
-      <c r="C3" s="474"/>
-      <c r="D3" s="474"/>
-      <c r="E3" s="474" t="s">
+      <c r="C3" s="480"/>
+      <c r="D3" s="480"/>
+      <c r="E3" s="480" t="s">
         <v>216</v>
       </c>
-      <c r="F3" s="474"/>
-      <c r="G3" s="474"/>
-      <c r="H3" s="474"/>
-      <c r="I3" s="475"/>
+      <c r="F3" s="480"/>
+      <c r="G3" s="480"/>
+      <c r="H3" s="480"/>
+      <c r="I3" s="481"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="25">
@@ -21653,7 +21647,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="219" t="s">
-        <v>1107</v>
+        <v>1101</v>
       </c>
       <c r="C15" s="219"/>
       <c r="D15" s="219"/>
@@ -21670,7 +21664,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="240" t="s">
-        <v>1094</v>
+        <v>1088</v>
       </c>
       <c r="C16" s="240"/>
       <c r="D16" s="240"/>
@@ -21794,7 +21788,7 @@
       <c r="C23" s="219"/>
       <c r="D23" s="219"/>
       <c r="E23" s="219" t="s">
-        <v>1086</v>
+        <v>1080</v>
       </c>
       <c r="F23" s="219"/>
       <c r="G23" s="219"/>
@@ -21845,7 +21839,7 @@
         <v>1</v>
       </c>
       <c r="B27" s="248" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="C27" s="248"/>
       <c r="D27" s="248"/>
@@ -21930,12 +21924,12 @@
         <v>6</v>
       </c>
       <c r="B32" s="210" t="s">
-        <v>1094</v>
+        <v>1088</v>
       </c>
       <c r="C32" s="210"/>
       <c r="D32" s="210"/>
       <c r="E32" s="219" t="s">
-        <v>1087</v>
+        <v>1081</v>
       </c>
       <c r="F32" s="219"/>
       <c r="G32" s="219"/>
@@ -21947,7 +21941,7 @@
         <v>7</v>
       </c>
       <c r="B33" s="219" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="C33" s="219"/>
       <c r="D33" s="219"/>
@@ -22118,18 +22112,18 @@
       <c r="A5" s="64">
         <v>3</v>
       </c>
-      <c r="B5" s="476" t="s">
+      <c r="B5" s="482" t="s">
         <v>917</v>
       </c>
-      <c r="C5" s="476"/>
-      <c r="D5" s="476"/>
-      <c r="E5" s="476" t="s">
+      <c r="C5" s="482"/>
+      <c r="D5" s="482"/>
+      <c r="E5" s="482" t="s">
         <v>918</v>
       </c>
-      <c r="F5" s="476"/>
-      <c r="G5" s="476"/>
-      <c r="H5" s="476"/>
-      <c r="I5" s="476"/>
+      <c r="F5" s="482"/>
+      <c r="G5" s="482"/>
+      <c r="H5" s="482"/>
+      <c r="I5" s="482"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="25">
@@ -22204,7 +22198,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="347" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="C10" s="347"/>
       <c r="D10" s="347"/>
@@ -22412,18 +22406,18 @@
       <c r="A23" s="64">
         <v>10</v>
       </c>
-      <c r="B23" s="477" t="s">
+      <c r="B23" s="483" t="s">
         <v>906</v>
       </c>
-      <c r="C23" s="477"/>
-      <c r="D23" s="477"/>
-      <c r="E23" s="477" t="s">
+      <c r="C23" s="483"/>
+      <c r="D23" s="483"/>
+      <c r="E23" s="483" t="s">
         <v>220</v>
       </c>
-      <c r="F23" s="477"/>
-      <c r="G23" s="477"/>
-      <c r="H23" s="477"/>
-      <c r="I23" s="477"/>
+      <c r="F23" s="483"/>
+      <c r="G23" s="483"/>
+      <c r="H23" s="483"/>
+      <c r="I23" s="483"/>
     </row>
     <row r="24" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="264"/>
@@ -22486,12 +22480,12 @@
         <v>2</v>
       </c>
       <c r="B28" s="345" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="C28" s="345"/>
       <c r="D28" s="345"/>
       <c r="E28" s="345" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="F28" s="345"/>
       <c r="G28" s="345"/>
@@ -22503,12 +22497,12 @@
         <v>3</v>
       </c>
       <c r="B29" s="347" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="C29" s="347"/>
       <c r="D29" s="347"/>
       <c r="E29" s="347" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="F29" s="347"/>
       <c r="G29" s="347"/>
@@ -22519,11 +22513,11 @@
       <c r="A30" s="25">
         <v>4</v>
       </c>
-      <c r="B30" s="478" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C30" s="478"/>
-      <c r="D30" s="478"/>
+      <c r="B30" s="484" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C30" s="484"/>
+      <c r="D30" s="484"/>
       <c r="E30" s="347" t="s">
         <v>921</v>
       </c>
@@ -22666,7 +22660,7 @@
       <c r="C39" s="345"/>
       <c r="D39" s="345"/>
       <c r="E39" s="345" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="F39" s="345"/>
       <c r="G39" s="345"/>
@@ -22734,7 +22728,7 @@
       <c r="C43" s="347"/>
       <c r="D43" s="347"/>
       <c r="E43" s="347" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="F43" s="347"/>
       <c r="G43" s="347"/>
@@ -23179,7 +23173,7 @@
         <v>8</v>
       </c>
       <c r="B21" s="219" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="C21" s="219"/>
       <c r="D21" s="219"/>
@@ -23314,7 +23308,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="270" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="C3" s="271"/>
       <c r="D3" s="273"/>
@@ -23749,7 +23743,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="301" t="s">
-        <v>1156</v>
+        <v>1150</v>
       </c>
       <c r="C30" s="302"/>
       <c r="D30" s="303"/>
@@ -23907,7 +23901,7 @@
         <v>3</v>
       </c>
       <c r="B40" s="301" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="C40" s="302"/>
       <c r="D40" s="303"/>
@@ -23941,7 +23935,7 @@
         <v>5</v>
       </c>
       <c r="B42" s="288" t="s">
-        <v>1095</v>
+        <v>1089</v>
       </c>
       <c r="C42" s="289"/>
       <c r="D42" s="290"/>
@@ -24340,12 +24334,12 @@
         <v>4</v>
       </c>
       <c r="B17" s="310" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="C17" s="310"/>
       <c r="D17" s="310"/>
       <c r="E17" s="310" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="F17" s="310"/>
       <c r="G17" s="310"/>
@@ -24374,7 +24368,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="310" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="C19" s="310"/>
       <c r="D19" s="310"/>
@@ -24755,7 +24749,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="219" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="C4" s="219"/>
       <c r="D4" s="219"/>
@@ -24913,7 +24907,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="240" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="C14" s="240"/>
       <c r="D14" s="240"/>
@@ -25003,7 +24997,7 @@
       <c r="C19" s="210"/>
       <c r="D19" s="210"/>
       <c r="E19" s="210" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="F19" s="210"/>
       <c r="G19" s="210"/>
@@ -25015,7 +25009,7 @@
         <v>7</v>
       </c>
       <c r="B20" s="210" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="C20" s="210"/>
       <c r="D20" s="210"/>
@@ -25590,12 +25584,12 @@
         <v>4</v>
       </c>
       <c r="B6" s="320" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="C6" s="320"/>
       <c r="D6" s="320"/>
       <c r="E6" s="320" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
       <c r="F6" s="320"/>
       <c r="G6" s="320"/>
@@ -25624,12 +25618,12 @@
         <v>6</v>
       </c>
       <c r="B8" s="320" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
       <c r="C8" s="320"/>
       <c r="D8" s="320"/>
       <c r="E8" s="320" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="F8" s="320"/>
       <c r="G8" s="320"/>
@@ -25658,12 +25652,12 @@
         <v>8</v>
       </c>
       <c r="B10" s="322" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="C10" s="322"/>
       <c r="D10" s="322"/>
       <c r="E10" s="322" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="F10" s="322"/>
       <c r="G10" s="322"/>
@@ -25735,12 +25729,12 @@
         <v>1</v>
       </c>
       <c r="B3" s="331" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="C3" s="331"/>
       <c r="D3" s="331"/>
       <c r="E3" s="331" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="F3" s="331"/>
       <c r="G3" s="331"/>
@@ -25949,7 +25943,7 @@
       <c r="C16" s="329"/>
       <c r="D16" s="329"/>
       <c r="E16" s="329" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F16" s="329"/>
       <c r="G16" s="329"/>
@@ -26029,7 +26023,7 @@
         <v>8</v>
       </c>
       <c r="B21" s="327" t="s">
-        <v>1137</v>
+        <v>1131</v>
       </c>
       <c r="C21" s="327"/>
       <c r="D21" s="327"/>
